--- a/src/main/webapp/data/pacientes_lab.xlsx
+++ b/src/main/webapp/data/pacientes_lab.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,42 +424,42 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1713031167</v>
+        <v>123132266</v>
       </c>
       <c r="B2" t="str">
-        <v>MOLINA TRUJILLO CRISTIAN</v>
+        <v>Moli</v>
       </c>
       <c r="C2" t="str">
-        <v>0001-11-11</v>
+        <v>0011-11-11</v>
       </c>
       <c r="D2" t="str">
         <v>Masculino</v>
       </c>
       <c r="E2" t="str">
-        <v>0995225612</v>
+        <v>11111</v>
       </c>
       <c r="F2" t="str">
-        <v>kristiandank@gmail.com</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>123456</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>123132266</v>
+        <v>222222222</v>
       </c>
       <c r="B3" t="str">
-        <v>Moli</v>
+        <v>222222</v>
       </c>
       <c r="C3" t="str">
-        <v>0011-11-11</v>
+        <v>0001-11-11</v>
       </c>
       <c r="D3" t="str">
         <v>Masculino</v>
       </c>
       <c r="E3" t="str">
-        <v>11111</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -470,19 +470,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>222222222</v>
+        <v>333333</v>
       </c>
       <c r="B4" t="str">
-        <v>222222</v>
+        <v>3333</v>
       </c>
       <c r="C4" t="str">
-        <v>0001-11-11</v>
+        <v>0001-01-01</v>
       </c>
       <c r="D4" t="str">
-        <v>Masculino</v>
+        <v>Femenino</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>ss</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -493,16 +493,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>333333</v>
+        <v>1713031165</v>
       </c>
       <c r="B5" t="str">
-        <v>3333</v>
+        <v>MOLINA MILTON</v>
       </c>
       <c r="C5" t="str">
-        <v>0001-01-01</v>
+        <v>2026-08-09</v>
       </c>
       <c r="D5" t="str">
-        <v>Femenino</v>
+        <v>Masculino</v>
       </c>
       <c r="E5" t="str">
         <v>ss</v>
@@ -511,35 +511,12 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1713031165</v>
-      </c>
-      <c r="B6" t="str">
-        <v>MOLINA MILTON</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2026-08-09</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Masculino</v>
-      </c>
-      <c r="E6" t="str">
-        <v>ss</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
         <v>ss</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>